--- a/data/gravel/Surly Grappler 2025.xlsx
+++ b/data/gravel/Surly Grappler 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5CE2D03-4C1C-E344-AB9F-9B0A7E5E6D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0DE5752-3698-184C-B747-AAB46A25CC82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9060" yWindow="500" windowWidth="19740" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -262,97 +262,97 @@
     <t>USD</t>
   </si>
   <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>X-Small</t>
+  </si>
+  <si>
+    <t>Small</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>X-Large</t>
+  </si>
+  <si>
+    <t>A. Effective Top Tube</t>
+  </si>
+  <si>
+    <t>B. Stand Over</t>
+  </si>
+  <si>
+    <t>C. Reach</t>
+  </si>
+  <si>
+    <t>D. Stack</t>
+  </si>
+  <si>
+    <t>E. Total Seat Tube Length</t>
+  </si>
+  <si>
+    <t>F. Headtube Length</t>
+  </si>
+  <si>
+    <t>G. Headtube Angle</t>
+  </si>
+  <si>
+    <t>H. Seat Tube Angle</t>
+  </si>
+  <si>
+    <t>I. BB Drop</t>
+  </si>
+  <si>
+    <t>K. Chainstay Length</t>
+  </si>
+  <si>
+    <t>L. Fork Length Axle to Crown</t>
+  </si>
+  <si>
+    <t>M. Fork Offset</t>
+  </si>
+  <si>
+    <t>N. Wheelbase</t>
+  </si>
+  <si>
+    <t>Crank Arm Length</t>
+  </si>
+  <si>
+    <t>Recommended Rider Height</t>
+  </si>
+  <si>
+    <t>142.0 - 151.0</t>
+  </si>
+  <si>
+    <t>152.0 - 164.0</t>
+  </si>
+  <si>
+    <t>165.0 - 174.0</t>
+  </si>
+  <si>
+    <t>175.0 - 184.0</t>
+  </si>
+  <si>
+    <t>internal</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>threaded 73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grappler </t>
+  </si>
+  <si>
+    <t>a8:g30</t>
+  </si>
+  <si>
     <t>142/148</t>
-  </si>
-  <si>
-    <t>Size</t>
-  </si>
-  <si>
-    <t>X-Small</t>
-  </si>
-  <si>
-    <t>Small</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Large</t>
-  </si>
-  <si>
-    <t>X-Large</t>
-  </si>
-  <si>
-    <t>A. Effective Top Tube</t>
-  </si>
-  <si>
-    <t>B. Stand Over</t>
-  </si>
-  <si>
-    <t>C. Reach</t>
-  </si>
-  <si>
-    <t>D. Stack</t>
-  </si>
-  <si>
-    <t>E. Total Seat Tube Length</t>
-  </si>
-  <si>
-    <t>F. Headtube Length</t>
-  </si>
-  <si>
-    <t>G. Headtube Angle</t>
-  </si>
-  <si>
-    <t>H. Seat Tube Angle</t>
-  </si>
-  <si>
-    <t>I. BB Drop</t>
-  </si>
-  <si>
-    <t>K. Chainstay Length</t>
-  </si>
-  <si>
-    <t>L. Fork Length Axle to Crown</t>
-  </si>
-  <si>
-    <t>M. Fork Offset</t>
-  </si>
-  <si>
-    <t>N. Wheelbase</t>
-  </si>
-  <si>
-    <t>Crank Arm Length</t>
-  </si>
-  <si>
-    <t>Recommended Rider Height</t>
-  </si>
-  <si>
-    <t>142.0 - 151.0</t>
-  </si>
-  <si>
-    <t>152.0 - 164.0</t>
-  </si>
-  <si>
-    <t>165.0 - 174.0</t>
-  </si>
-  <si>
-    <t>175.0 - 184.0</t>
-  </si>
-  <si>
-    <t>internal</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>threaded 73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grappler </t>
-  </si>
-  <si>
-    <t>a8:g30</t>
   </si>
 </sst>
 </file>
@@ -711,7 +711,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -743,7 +743,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -751,22 +751,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" t="s">
         <v>81</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>82</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>83</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>84</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>85</v>
-      </c>
-      <c r="G8" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -774,7 +774,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C9">
         <v>560</v>
@@ -797,7 +797,7 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C10">
         <v>719</v>
@@ -820,7 +820,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C11">
         <v>381</v>
@@ -843,7 +843,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C12">
         <v>585</v>
@@ -866,7 +866,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C13">
         <v>316</v>
@@ -889,7 +889,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C14">
         <v>160</v>
@@ -912,7 +912,7 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C15">
         <v>69.5</v>
@@ -935,7 +935,7 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C16">
         <v>73</v>
@@ -958,7 +958,7 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C17">
         <v>50</v>
@@ -981,7 +981,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C18">
         <v>425</v>
@@ -1004,7 +1004,7 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C19">
         <v>420</v>
@@ -1027,7 +1027,7 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C20">
         <v>50</v>
@@ -1050,7 +1050,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C21">
         <v>1057</v>
@@ -1073,7 +1073,7 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C22">
         <v>170</v>
@@ -1259,22 +1259,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
+        <v>101</v>
+      </c>
+      <c r="D31" t="s">
         <v>102</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" t="s">
         <v>104</v>
-      </c>
-      <c r="F31" t="s">
-        <v>105</v>
       </c>
       <c r="G31">
         <v>185</v>
       </c>
       <c r="H31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
@@ -1368,7 +1368,7 @@
         <v>46</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -1384,7 +1384,7 @@
         <v>48</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
@@ -1405,7 +1405,7 @@
         <v>51</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -1452,7 +1452,7 @@
         <v>58</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -1499,7 +1499,7 @@
         <v>65</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/Surly Grappler 2025.xlsx
+++ b/data/gravel/Surly Grappler 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0DE5752-3698-184C-B747-AAB46A25CC82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{481F2861-07E5-094D-A54A-BD68C1D3FC4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9060" yWindow="500" windowWidth="19740" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -352,7 +352,7 @@
     <t>a8:g30</t>
   </si>
   <si>
-    <t>142/148</t>
+    <t>142/148 gnot boost</t>
   </si>
 </sst>
 </file>

--- a/data/gravel/Surly Grappler 2025.xlsx
+++ b/data/gravel/Surly Grappler 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{481F2861-07E5-094D-A54A-BD68C1D3FC4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DBA75C5-C276-0944-AA63-37A2A1D4F1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9060" yWindow="500" windowWidth="19740" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -353,13 +353,16 @@
   </si>
   <si>
     <t>142/148 gnot boost</t>
+  </si>
+  <si>
+    <t>https://surlybikes.com/cdn/shop/articles/Surly_Grappler_Blog-Header-2000x1333_f8c4fa78-d8d5-482d-93b3-a3505fcc4ce6.jpg?v=1742483763&amp;width=720</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -368,6 +371,13 @@
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
+      <name val="Futura"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="14"/>
+      <color theme="10"/>
       <name val="Futura"/>
       <family val="2"/>
     </font>
@@ -389,15 +399,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -738,6 +751,11 @@
         <v>78</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
@@ -1542,6 +1560,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{13DE5DEB-E7C5-B647-8E66-5441734D7F0C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/data/gravel/Surly Grappler 2025.xlsx
+++ b/data/gravel/Surly Grappler 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DBA75C5-C276-0944-AA63-37A2A1D4F1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7844C908-02B2-7E4F-A184-E22EB06842BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9060" yWindow="500" windowWidth="19740" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -356,6 +356,12 @@
   </si>
   <si>
     <t>https://surlybikes.com/cdn/shop/articles/Surly_Grappler_Blog-Header-2000x1333_f8c4fa78-d8d5-482d-93b3-a3505fcc4ce6.jpg?v=1742483763&amp;width=720</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Bloomington, Minnesota, USA</t>
   </si>
 </sst>
 </file>
@@ -705,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1559,6 +1565,14 @@
         <v>79</v>
       </c>
     </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>112</v>
+      </c>
+      <c r="B71" t="s">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B6" r:id="rId1" xr:uid="{13DE5DEB-E7C5-B647-8E66-5441734D7F0C}"/>

--- a/data/gravel/Surly Grappler 2025.xlsx
+++ b/data/gravel/Surly Grappler 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7844C908-02B2-7E4F-A184-E22EB06842BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40479A9-DAEF-A24D-AB3F-F9B35C3DC5BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9060" yWindow="500" windowWidth="19740" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="120">
   <si>
     <t>brand</t>
   </si>
@@ -362,6 +362,24 @@
   </si>
   <si>
     <t>Bloomington, Minnesota, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -711,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1405,171 +1423,201 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>48</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>50</v>
-      </c>
-      <c r="B49">
-        <v>30.9</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>51</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>52</v>
-      </c>
-      <c r="B51">
-        <v>38</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>53</v>
-      </c>
-      <c r="B52">
-        <v>39</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>54</v>
-      </c>
-      <c r="B53">
-        <v>203</v>
+        <v>48</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>50</v>
+      </c>
+      <c r="B55">
+        <v>30.9</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>58</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>105</v>
+        <v>52</v>
+      </c>
+      <c r="B57">
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="B58">
+        <v>39</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="B59">
+        <v>203</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>61</v>
-      </c>
-      <c r="B60">
-        <v>2</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>62</v>
-      </c>
-      <c r="B61">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>64</v>
-      </c>
-      <c r="B63">
-        <v>3</v>
+        <v>58</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>65</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>61</v>
+      </c>
+      <c r="B66">
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B67">
-        <v>849</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>69</v>
-      </c>
-      <c r="B68">
-        <v>1999</v>
+        <v>63</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="B69">
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>68</v>
+      </c>
+      <c r="B73">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>69</v>
+      </c>
+      <c r="B74">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>71</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>112</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B77" t="s">
         <v>113</v>
       </c>
     </row>
